--- a/sheets/국악이꽃피는나무/검수/진도아리랑.xlsx
+++ b/sheets/국악이꽃피는나무/검수/진도아리랑.xlsx
@@ -7650,7 +7650,7 @@
       <c r="J5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南j
+南
 –</t>
         </is>
       </c>
@@ -7827,7 +7827,7 @@
       <c r="J7" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南j</t>
+南</t>
         </is>
       </c>
       <c r="K7" s="29" t="inlineStr">
@@ -7890,7 +7890,7 @@
       <c r="E8" s="26"/>
       <c r="F8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 △</t>
         </is>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M8" s="28" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="N8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 △</t>
         </is>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 汰</t>
         </is>
@@ -8079,7 +8079,7 @@
       <c r="F10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南j
+南
 –</t>
         </is>
       </c>
@@ -8091,7 +8091,7 @@
       <c r="H10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南j
+南
 –</t>
         </is>
       </c>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="J10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 林</t>
         </is>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="L10" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 c汰</t>
         </is>
@@ -8127,7 +8127,7 @@
       <c r="N10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南j
+南
 –</t>
         </is>
       </c>
@@ -8139,7 +8139,7 @@
       <c r="P10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南j
+南
 –</t>
         </is>
       </c>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I11" s="28" t="inlineStr">
@@ -8199,7 +8199,7 @@
       <c r="K11" s="26"/>
       <c r="L11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M11" s="28" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="P11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q11" s="28" t="inlineStr">
@@ -8867,7 +8867,7 @@
       <c r="E22" s="26"/>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 △</t>
         </is>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="N22" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j
+          <t xml:space="preserve">南
 –
 △</t>
         </is>
@@ -9018,7 +9018,7 @@
       <c r="F24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南j
+南
 –</t>
         </is>
       </c>
@@ -9030,7 +9030,7 @@
       <c r="H24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南j
+南
 –</t>
         </is>
       </c>
@@ -9066,7 +9066,7 @@
       <c r="N24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-南j
+南
 –</t>
         </is>
       </c>
@@ -9078,7 +9078,7 @@
       <c r="P24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-南j
+南
 –</t>
         </is>
       </c>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H25" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I25" s="28" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="P25" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">南j</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q25" s="28" t="inlineStr">

--- a/sheets/국악이꽃피는나무/검수/진도아리랑.xlsx
+++ b/sheets/국악이꽃피는나무/검수/진도아리랑.xlsx
@@ -8315,7 +8315,7 @@
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K13" s="25" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O13" s="25" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K27" s="25" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="N27" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="O27" s="25" t="inlineStr">

--- a/sheets/국악이꽃피는나무/검수/진도아리랑.xlsx
+++ b/sheets/국악이꽃피는나무/검수/진도아리랑.xlsx
@@ -7381,28 +7381,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="67.8" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="100.96" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="100.96" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="100.96" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="100.96" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="100.96" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="100.96" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="100.96" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="100.96" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="100.96" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="100.96" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="100.96" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="100.96" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="67.8" customHeight="true">
+    <row r="16" ht="64.52" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="100.96" customHeight="true">
+    <row r="17" ht="96.05" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="100.96" customHeight="true">
+    <row r="18" ht="96.05" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="25"/>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="100.96" customHeight="true">
+    <row r="19" ht="96.05" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="26"/>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="100.96" customHeight="true">
+    <row r="20" ht="96.05" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="100.96" customHeight="true">
+    <row r="21" ht="96.05" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -8859,7 +8859,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="100.96" customHeight="true">
+    <row r="22" ht="96.05" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -8932,7 +8932,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="100.96" customHeight="true">
+    <row r="23" ht="96.05" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="100.96" customHeight="true">
+    <row r="24" ht="96.05" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="100.96" customHeight="true">
+    <row r="25" ht="96.05" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="26"/>
@@ -9153,7 +9153,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="100.96" customHeight="true">
+    <row r="26" ht="96.05" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -9220,7 +9220,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="100.96" customHeight="true">
+    <row r="27" ht="96.05" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="25"/>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="100.96" customHeight="true">
+    <row r="28" ht="96.05" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="26"/>
@@ -9361,7 +9361,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
